--- a/resources/eduction/pii/edk_samples/resources/pii_table_mode/extras/PII_table.xlsx
+++ b/resources/eduction/pii/edk_samples/resources/pii_table_mode/extras/PII_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MicroFocus\IDOLServer-12.13.0\EductionGrammars_12.13.0\pii\edk_samples\resources\pii_table_mode\extras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://opentextcorporation-my.sharepoint.com/personal/jblank_opentext_com/Documents/_Customers/Prospects/Datox.ai/Demo/pii_table_mode/extras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE3A4DB-8EB3-4900-B9D6-C827669298F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6AE3A4DB-8EB3-4900-B9D6-C827669298F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D40D74-5763-4005-9C75-9CAAD6628A0E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10950" yWindow="150" windowWidth="18225" windowHeight="14640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1- sensitive data" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>223-11-4854</t>
+  </si>
+  <si>
+    <t>Social Security Number</t>
   </si>
 </sst>
 </file>
@@ -423,15 +426,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -459,7 +462,7 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -473,7 +476,7 @@
         <v>43780</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>8</v>
       </c>
@@ -484,7 +487,7 @@
         <v>44491</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -503,16 +506,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8381FDC1-8385-4142-9B35-FA8B8E8D22A2}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,7 +523,7 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -529,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -546,7 +549,7 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -560,7 +563,7 @@
         <v>43780</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -574,7 +577,7 @@
         <v>44491</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -596,20 +599,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA3AE37C-9222-425B-9FA8-74D8AF866BE6}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -623,7 +626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -637,7 +640,7 @@
         <v>43831</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -651,7 +654,7 @@
         <v>43780</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>16</v>
       </c>
@@ -662,7 +665,7 @@
         <v>44491</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
